--- a/artfynd/A 21476-2026 artfynd.xlsx
+++ b/artfynd/A 21476-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109703307</v>
+        <v>109634524</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474707.6484739565</v>
+        <v>475298</v>
       </c>
       <c r="R2" t="n">
-        <v>6787342.323948846</v>
+        <v>6787764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109702058</v>
+        <v>110822431</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474707.6484739565</v>
+        <v>475310</v>
       </c>
       <c r="R3" t="n">
-        <v>6787342.323948846</v>
+        <v>6787766</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109722389</v>
+        <v>110822520</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -956,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474643.8270203338</v>
+        <v>475298</v>
       </c>
       <c r="R4" t="n">
-        <v>6787324.477080638</v>
+        <v>6787764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,47 +977,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109722330</v>
+        <v>109703650</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474642.5049785853</v>
+        <v>475119</v>
       </c>
       <c r="R5" t="n">
-        <v>6787141.409512092</v>
+        <v>6787598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,6 +1060,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109722391</v>
+        <v>109722347</v>
       </c>
       <c r="B6" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474669.5662873844</v>
+        <v>474599</v>
       </c>
       <c r="R6" t="n">
-        <v>6786946.082068373</v>
+        <v>6787312</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,22 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1162,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1266,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109722363</v>
+        <v>109703307</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,27 +1191,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474589.4785734449</v>
+        <v>474708</v>
       </c>
       <c r="R7" t="n">
-        <v>6786882.096053024</v>
+        <v>6787342</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,22 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1383,51 +1285,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109722337</v>
+        <v>109722352</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1435,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474589.4785734449</v>
+        <v>474605</v>
       </c>
       <c r="R8" t="n">
-        <v>6786882.096053024</v>
+        <v>6787314</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,22 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,15 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109722359</v>
+        <v>109702058</v>
       </c>
       <c r="B9" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1551,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474594.4261475292</v>
+        <v>474708</v>
       </c>
       <c r="R9" t="n">
-        <v>6786898.92426512</v>
+        <v>6787342</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1581,22 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,6 +1485,943 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>109722389</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>474644</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6787325</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110894750</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>474592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6787268</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>109722330</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>474642</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6787142</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>109722407</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>474613</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6786946</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>109722391</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>474670</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6786946</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>109722359</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>474594</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6786899</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109722363</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>474590</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6786882</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>109751207</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>474594</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6786899</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>109722337</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>474590</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6786882</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2001-06-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21476-2026 artfynd.xlsx
+++ b/artfynd/A 21476-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109634524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110822431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110822520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109703650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722347</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722352</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722389</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110894750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109703307</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109702058</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722330</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,6 +1952,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722407</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722391</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722359</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722363</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751207</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,8 +2507,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109722337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>